--- a/EcoFin/gold.xlsx
+++ b/EcoFin/gold.xlsx
@@ -11,6 +11,17 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -57,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -355,1150 +366,1162 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B142"/>
+  <dimension ref="A1:B144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>41974</v>
+    <row r="1" spans="1:2" s="2" customFormat="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1">
+        <v>42004</v>
       </c>
       <c r="B2">
         <v>1183.900024414062</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2">
-        <v>42005</v>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1">
+        <v>42035</v>
       </c>
       <c r="B3">
         <v>1278.5</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2">
-        <v>42036</v>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1">
+        <v>42063</v>
       </c>
       <c r="B4">
         <v>1212.599975585938</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2">
-        <v>42064</v>
+    <row r="5" spans="1:2">
+      <c r="A5" s="1">
+        <v>42094</v>
       </c>
       <c r="B5">
         <v>1183.099975585938</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2">
-        <v>42095</v>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1">
+        <v>42124</v>
       </c>
       <c r="B6">
         <v>1182.400024414062</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2">
-        <v>42125</v>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1">
+        <v>42155</v>
       </c>
       <c r="B7">
         <v>1189.400024414062</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>42156</v>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1">
+        <v>42185</v>
       </c>
       <c r="B8">
         <v>1171.5</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2">
-        <v>42186</v>
+    <row r="9" spans="1:2">
+      <c r="A9" s="1">
+        <v>42216</v>
       </c>
       <c r="B9">
         <v>1094.900024414062</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>42217</v>
+    <row r="10" spans="1:2">
+      <c r="A10" s="1">
+        <v>42247</v>
       </c>
       <c r="B10">
         <v>1131.599975585938</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2">
-        <v>42248</v>
+    <row r="11" spans="1:2">
+      <c r="A11" s="1">
+        <v>42277</v>
       </c>
       <c r="B11">
         <v>1115.5</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>42278</v>
+    <row r="12" spans="1:2">
+      <c r="A12" s="1">
+        <v>42308</v>
       </c>
       <c r="B12">
         <v>1141.5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2">
-        <v>42309</v>
+    <row r="13" spans="1:2">
+      <c r="A13" s="1">
+        <v>42338</v>
       </c>
       <c r="B13">
         <v>1065.800048828125</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>42339</v>
+    <row r="14" spans="1:2">
+      <c r="A14" s="1">
+        <v>42369</v>
       </c>
       <c r="B14">
         <v>1060.300048828125</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2">
-        <v>42370</v>
+    <row r="15" spans="1:2">
+      <c r="A15" s="1">
+        <v>42400</v>
       </c>
       <c r="B15">
         <v>1116.400024414062</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>42401</v>
+    <row r="16" spans="1:2">
+      <c r="A16" s="1">
+        <v>42429</v>
       </c>
       <c r="B16">
         <v>1233.900024414062</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2">
-        <v>42430</v>
+    <row r="17" spans="1:2">
+      <c r="A17" s="1">
+        <v>42460</v>
       </c>
       <c r="B17">
         <v>1234.199951171875</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>42461</v>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1">
+        <v>42490</v>
       </c>
       <c r="B18">
         <v>1289.199951171875</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2">
-        <v>42491</v>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1">
+        <v>42521</v>
       </c>
       <c r="B19">
         <v>1214.800048828125</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>42522</v>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1">
+        <v>42551</v>
       </c>
       <c r="B20">
         <v>1318.400024414062</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2">
-        <v>42552</v>
+    <row r="21" spans="1:2">
+      <c r="A21" s="1">
+        <v>42582</v>
       </c>
       <c r="B21">
         <v>1349</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2">
-        <v>42583</v>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1">
+        <v>42613</v>
       </c>
       <c r="B22">
         <v>1306.900024414062</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2">
-        <v>42614</v>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1">
+        <v>42643</v>
       </c>
       <c r="B23">
         <v>1313.300048828125</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2">
-        <v>42644</v>
+    <row r="24" spans="1:2">
+      <c r="A24" s="1">
+        <v>42674</v>
       </c>
       <c r="B24">
         <v>1271.5</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2">
-        <v>42675</v>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1">
+        <v>42704</v>
       </c>
       <c r="B25">
         <v>1170.800048828125</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2">
-        <v>42705</v>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1">
+        <v>42735</v>
       </c>
       <c r="B26">
         <v>1150</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2">
-        <v>42736</v>
+    <row r="27" spans="1:2">
+      <c r="A27" s="1">
+        <v>42766</v>
       </c>
       <c r="B27">
         <v>1208.599975585938</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2">
-        <v>42767</v>
+    <row r="28" spans="1:2">
+      <c r="A28" s="1">
+        <v>42794</v>
       </c>
       <c r="B28">
         <v>1252.599975585938</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2">
-        <v>42795</v>
+    <row r="29" spans="1:2">
+      <c r="A29" s="1">
+        <v>42825</v>
       </c>
       <c r="B29">
         <v>1247.300048828125</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2">
-        <v>42826</v>
+    <row r="30" spans="1:2">
+      <c r="A30" s="1">
+        <v>42855</v>
       </c>
       <c r="B30">
         <v>1266.099975585938</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2">
-        <v>42856</v>
+    <row r="31" spans="1:2">
+      <c r="A31" s="1">
+        <v>42886</v>
       </c>
       <c r="B31">
         <v>1272</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2">
-        <v>42887</v>
+    <row r="32" spans="1:2">
+      <c r="A32" s="1">
+        <v>42916</v>
       </c>
       <c r="B32">
         <v>1240.699951171875</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>42917</v>
+    <row r="33" spans="1:2">
+      <c r="A33" s="1">
+        <v>42947</v>
       </c>
       <c r="B33">
         <v>1266.599975585938</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>42948</v>
+    <row r="34" spans="1:2">
+      <c r="A34" s="1">
+        <v>42978</v>
       </c>
       <c r="B34">
         <v>1316.199951171875</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2">
-        <v>42979</v>
+    <row r="35" spans="1:2">
+      <c r="A35" s="1">
+        <v>43008</v>
       </c>
       <c r="B35">
         <v>1281.5</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2">
-        <v>43009</v>
+    <row r="36" spans="1:2">
+      <c r="A36" s="1">
+        <v>43039</v>
       </c>
       <c r="B36">
         <v>1267</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2">
-        <v>43040</v>
+    <row r="37" spans="1:2">
+      <c r="A37" s="1">
+        <v>43069</v>
       </c>
       <c r="B37">
         <v>1273.199951171875</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2">
-        <v>43070</v>
+    <row r="38" spans="1:2">
+      <c r="A38" s="1">
+        <v>43100</v>
       </c>
       <c r="B38">
         <v>1306.300048828125</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2">
-        <v>43101</v>
+    <row r="39" spans="1:2">
+      <c r="A39" s="1">
+        <v>43131</v>
       </c>
       <c r="B39">
         <v>1339</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2">
-        <v>43132</v>
+    <row r="40" spans="1:2">
+      <c r="A40" s="1">
+        <v>43159</v>
       </c>
       <c r="B40">
         <v>1315.5</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2">
-        <v>43160</v>
+    <row r="41" spans="1:2">
+      <c r="A41" s="1">
+        <v>43190</v>
       </c>
       <c r="B41">
         <v>1322.800048828125</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2">
-        <v>43191</v>
+    <row r="42" spans="1:2">
+      <c r="A42" s="1">
+        <v>43220</v>
       </c>
       <c r="B42">
         <v>1316.199951171875</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2">
-        <v>43221</v>
+    <row r="43" spans="1:2">
+      <c r="A43" s="1">
+        <v>43251</v>
       </c>
       <c r="B43">
         <v>1300.099975585938</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2">
-        <v>43252</v>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1">
+        <v>43281</v>
       </c>
       <c r="B44">
         <v>1251.300048828125</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2">
-        <v>43282</v>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1">
+        <v>43312</v>
       </c>
       <c r="B45">
         <v>1223.699951171875</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2">
-        <v>43313</v>
+    <row r="46" spans="1:2">
+      <c r="A46" s="1">
+        <v>43343</v>
       </c>
       <c r="B46">
         <v>1200.300048828125</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2">
-        <v>43344</v>
+    <row r="47" spans="1:2">
+      <c r="A47" s="1">
+        <v>43373</v>
       </c>
       <c r="B47">
         <v>1191.5</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2">
-        <v>43374</v>
+    <row r="48" spans="1:2">
+      <c r="A48" s="1">
+        <v>43404</v>
       </c>
       <c r="B48">
         <v>1212.300048828125</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2">
-        <v>43405</v>
+    <row r="49" spans="1:2">
+      <c r="A49" s="1">
+        <v>43434</v>
       </c>
       <c r="B49">
         <v>1220.199951171875</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2">
-        <v>43435</v>
+    <row r="50" spans="1:2">
+      <c r="A50" s="1">
+        <v>43465</v>
       </c>
       <c r="B50">
         <v>1278.300048828125</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2">
-        <v>43466</v>
+    <row r="51" spans="1:2">
+      <c r="A51" s="1">
+        <v>43496</v>
       </c>
       <c r="B51">
         <v>1319.699951171875</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2">
-        <v>43497</v>
+    <row r="52" spans="1:2">
+      <c r="A52" s="1">
+        <v>43524</v>
       </c>
       <c r="B52">
         <v>1312.800048828125</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2">
-        <v>43525</v>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1">
+        <v>43555</v>
       </c>
       <c r="B53">
         <v>1293</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2">
-        <v>43556</v>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1">
+        <v>43585</v>
       </c>
       <c r="B54">
         <v>1282.800048828125</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2">
-        <v>43586</v>
+    <row r="55" spans="1:2">
+      <c r="A55" s="1">
+        <v>43616</v>
       </c>
       <c r="B55">
         <v>1305.800048828125</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2">
-        <v>43617</v>
+    <row r="56" spans="1:2">
+      <c r="A56" s="1">
+        <v>43646</v>
       </c>
       <c r="B56">
         <v>1409.699951171875</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2">
-        <v>43647</v>
+    <row r="57" spans="1:2">
+      <c r="A57" s="1">
+        <v>43677</v>
       </c>
       <c r="B57">
         <v>1426.099975585938</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2">
-        <v>43678</v>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1">
+        <v>43708</v>
       </c>
       <c r="B58">
         <v>1519.099975585938</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2">
-        <v>43709</v>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1">
+        <v>43738</v>
       </c>
       <c r="B59">
         <v>1465.699951171875</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2">
-        <v>43739</v>
+    <row r="60" spans="1:2">
+      <c r="A60" s="1">
+        <v>43769</v>
       </c>
       <c r="B60">
         <v>1511.400024414062</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2">
-        <v>43770</v>
+    <row r="61" spans="1:2">
+      <c r="A61" s="1">
+        <v>43799</v>
       </c>
       <c r="B61">
         <v>1465.599975585938</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2">
-        <v>43800</v>
+    <row r="62" spans="1:2">
+      <c r="A62" s="1">
+        <v>43830</v>
       </c>
       <c r="B62">
         <v>1519.5</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2">
-        <v>43831</v>
+    <row r="63" spans="1:2">
+      <c r="A63" s="1">
+        <v>43861</v>
       </c>
       <c r="B63">
         <v>1582.900024414062</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2">
-        <v>43862</v>
+    <row r="64" spans="1:2">
+      <c r="A64" s="1">
+        <v>43890</v>
       </c>
       <c r="B64">
         <v>1564.099975585938</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2">
-        <v>43891</v>
+    <row r="65" spans="1:2">
+      <c r="A65" s="1">
+        <v>43921</v>
       </c>
       <c r="B65">
         <v>1583.400024414062</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2">
-        <v>43922</v>
+    <row r="66" spans="1:2">
+      <c r="A66" s="1">
+        <v>43951</v>
       </c>
       <c r="B66">
         <v>1684.199951171875</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2">
-        <v>43952</v>
+    <row r="67" spans="1:2">
+      <c r="A67" s="1">
+        <v>43982</v>
       </c>
       <c r="B67">
-        <v>1736.900024414062</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2">
-        <v>43983</v>
+        <v>1751.699951171875</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="1">
+        <v>44012</v>
       </c>
       <c r="B68">
-        <v>1793</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2">
-        <v>44013</v>
+        <v>1800.5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="1">
+        <v>44043</v>
       </c>
       <c r="B69">
         <v>1962.800048828125</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>44044</v>
+    <row r="70" spans="1:2">
+      <c r="A70" s="1">
+        <v>44074</v>
       </c>
       <c r="B70">
-        <v>1967.599975585938</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>44075</v>
+        <v>1978.599975585938</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="1">
+        <v>44104</v>
       </c>
       <c r="B71">
-        <v>1887.5</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>44105</v>
+        <v>1895.5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="1">
+        <v>44135</v>
       </c>
       <c r="B72">
-        <v>1877.400024414062</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>44136</v>
+        <v>1879.900024414062</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="1">
+        <v>44165</v>
       </c>
       <c r="B73">
         <v>1775.699951171875</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>44166</v>
+    <row r="74" spans="1:2">
+      <c r="A74" s="1">
+        <v>44196</v>
       </c>
       <c r="B74">
-        <v>1893.099975585938</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>44197</v>
+        <v>1895.099975585938</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1">
+        <v>44227</v>
       </c>
       <c r="B75">
         <v>1847.300048828125</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2">
-        <v>44228</v>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1">
+        <v>44255</v>
       </c>
       <c r="B76">
-        <v>1728.099975585938</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="2">
-        <v>44256</v>
+        <v>1728.800048828125</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="1">
+        <v>44286</v>
       </c>
       <c r="B77">
         <v>1713.800048828125</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2">
-        <v>44287</v>
+    <row r="78" spans="1:2">
+      <c r="A78" s="1">
+        <v>44316</v>
       </c>
       <c r="B78">
-        <v>1767.300048828125</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="2">
-        <v>44317</v>
+        <v>1767.699951171875</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="1">
+        <v>44347</v>
       </c>
       <c r="B79">
         <v>1902.5</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2">
-        <v>44348</v>
+    <row r="80" spans="1:2">
+      <c r="A80" s="1">
+        <v>44377</v>
       </c>
       <c r="B80">
-        <v>1770.800048828125</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2">
-        <v>44378</v>
+        <v>1771.599975585938</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1">
+        <v>44408</v>
       </c>
       <c r="B81">
         <v>1812.599975585938</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2">
-        <v>44409</v>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1">
+        <v>44439</v>
       </c>
       <c r="B82">
-        <v>1815</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2">
-        <v>44440</v>
+        <v>1818.099975585938</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="1">
+        <v>44469</v>
       </c>
       <c r="B83">
-        <v>1755.300048828125</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2">
-        <v>44470</v>
+        <v>1757</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="1">
+        <v>44500</v>
       </c>
       <c r="B84">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2">
-        <v>44501</v>
+        <v>1783.900024414062</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="1">
+        <v>44530</v>
       </c>
       <c r="B85">
         <v>1773.599975585938</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>44531</v>
+    <row r="86" spans="1:2">
+      <c r="A86" s="1">
+        <v>44561</v>
       </c>
       <c r="B86">
-        <v>1827.5</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>44562</v>
+        <v>1828.599975585938</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" s="1">
+        <v>44592</v>
       </c>
       <c r="B87">
         <v>1795</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>44593</v>
+    <row r="88" spans="1:2">
+      <c r="A88" s="1">
+        <v>44620</v>
       </c>
       <c r="B88">
-        <v>1899.400024414062</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2">
-        <v>44621</v>
+        <v>1900.699951171875</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" s="1">
+        <v>44651</v>
       </c>
       <c r="B89">
         <v>1949.199951171875</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2">
-        <v>44652</v>
+    <row r="90" spans="1:2">
+      <c r="A90" s="1">
+        <v>44681</v>
       </c>
       <c r="B90">
-        <v>1909.300048828125</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2">
-        <v>44682</v>
+        <v>1911.699951171875</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" s="1">
+        <v>44712</v>
       </c>
       <c r="B91">
         <v>1842.699951171875</v>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2">
-        <v>44713</v>
+    <row r="92" spans="1:2">
+      <c r="A92" s="1">
+        <v>44742</v>
       </c>
       <c r="B92">
-        <v>1804.099975585938</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2">
-        <v>44743</v>
+        <v>1807.300048828125</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" s="1">
+        <v>44773</v>
       </c>
       <c r="B93">
         <v>1762.900024414062</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2">
-        <v>44774</v>
+    <row r="94" spans="1:2">
+      <c r="A94" s="1">
+        <v>44804</v>
       </c>
       <c r="B94">
-        <v>1712.800048828125</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2">
-        <v>44805</v>
+        <v>1726.199951171875</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" s="1">
+        <v>44834</v>
       </c>
       <c r="B95">
-        <v>1662.400024414062</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2">
-        <v>44835</v>
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" s="1">
+        <v>44865</v>
       </c>
       <c r="B96">
-        <v>1635.900024414062</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2">
-        <v>44866</v>
+        <v>1640.699951171875</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" s="1">
+        <v>44895</v>
       </c>
       <c r="B97">
         <v>1746</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2">
-        <v>44896</v>
+    <row r="98" spans="1:2">
+      <c r="A98" s="1">
+        <v>44926</v>
       </c>
       <c r="B98">
-        <v>1819.699951171875</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2">
-        <v>44927</v>
+        <v>1826.199951171875</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" s="1">
+        <v>44957</v>
       </c>
       <c r="B99">
         <v>1929.5</v>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2">
-        <v>44958</v>
+    <row r="100" spans="1:2">
+      <c r="A100" s="1">
+        <v>44985</v>
       </c>
       <c r="B100">
-        <v>1828.900024414062</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2">
-        <v>44986</v>
+        <v>1836.699951171875</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" s="1">
+        <v>45016</v>
       </c>
       <c r="B101">
         <v>1969</v>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2">
-        <v>45017</v>
+    <row r="102" spans="1:2">
+      <c r="A102" s="1">
+        <v>45046</v>
       </c>
       <c r="B102">
-        <v>1990.099975585938</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2">
-        <v>45047</v>
+        <v>1999.099975585938</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" s="1">
+        <v>45077</v>
       </c>
       <c r="B103">
         <v>1963.900024414062</v>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2">
-        <v>45078</v>
+    <row r="104" spans="1:2">
+      <c r="A104" s="1">
+        <v>45107</v>
       </c>
       <c r="B104">
-        <v>1921.099975585938</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2">
-        <v>45108</v>
+        <v>1929.400024414062</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="1">
+        <v>45138</v>
       </c>
       <c r="B105">
         <v>1970.5</v>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2">
-        <v>45139</v>
+    <row r="106" spans="1:2">
+      <c r="A106" s="1">
+        <v>45169</v>
       </c>
       <c r="B106">
-        <v>1938.199951171875</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2">
-        <v>45170</v>
+        <v>1965.900024414062</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" s="1">
+        <v>45199</v>
       </c>
       <c r="B107">
-        <v>1848.099975585938</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2">
-        <v>45200</v>
+        <v>1866.099975585938</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" s="1">
+        <v>45230</v>
       </c>
       <c r="B108">
-        <v>1985.199951171875</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2">
-        <v>45231</v>
+        <v>1994.300048828125</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" s="1">
+        <v>45260</v>
       </c>
       <c r="B109">
         <v>2038.099975585938</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2">
-        <v>45261</v>
+    <row r="110" spans="1:2">
+      <c r="A110" s="1">
+        <v>45291</v>
       </c>
       <c r="B110">
-        <v>2062.39990234375</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2">
-        <v>45292</v>
+        <v>2071.800048828125</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" s="1">
+        <v>45322</v>
       </c>
       <c r="B111">
         <v>2048.39990234375</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2">
-        <v>45323</v>
+    <row r="112" spans="1:2">
+      <c r="A112" s="1">
+        <v>45351</v>
       </c>
       <c r="B112">
-        <v>2045.699951171875</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="2">
-        <v>45352</v>
+        <v>2054.699951171875</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" s="1">
+        <v>45382</v>
       </c>
       <c r="B113">
         <v>2217.39990234375</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2">
-        <v>45383</v>
+    <row r="114" spans="1:2">
+      <c r="A114" s="1">
+        <v>45412</v>
       </c>
       <c r="B114">
-        <v>2291.39990234375</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2">
-        <v>45413</v>
+        <v>2302.89990234375</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="1">
+        <v>45443</v>
       </c>
       <c r="B115">
         <v>2322.89990234375</v>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2">
-        <v>45444</v>
+    <row r="116" spans="1:2">
+      <c r="A116" s="1">
+        <v>45473</v>
       </c>
       <c r="B116">
-        <v>2327.699951171875</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2">
-        <v>45474</v>
+        <v>2339.60009765625</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" s="1">
+        <v>45504</v>
       </c>
       <c r="B117">
         <v>2426.5</v>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2">
-        <v>45505</v>
+    <row r="118" spans="1:2">
+      <c r="A118" s="1">
+        <v>45535</v>
       </c>
       <c r="B118">
-        <v>2493.800048828125</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2">
-        <v>45536</v>
+        <v>2527.60009765625</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" s="1">
+        <v>45565</v>
       </c>
       <c r="B119">
-        <v>2636.10009765625</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2">
-        <v>45566</v>
+        <v>2659.39990234375</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" s="1">
+        <v>45596</v>
       </c>
       <c r="B120">
-        <v>2738.300048828125</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2">
-        <v>45597</v>
+        <v>2749.300048828125</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" s="1">
+        <v>45626</v>
       </c>
       <c r="B121">
         <v>2657</v>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2">
-        <v>45627</v>
+    <row r="122" spans="1:2">
+      <c r="A122" s="1">
+        <v>45657</v>
       </c>
       <c r="B122">
-        <v>2629.199951171875</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2">
-        <v>45658</v>
+        <v>2641</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" s="1">
+        <v>45688</v>
       </c>
       <c r="B123">
         <v>2812.5</v>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2">
-        <v>45689</v>
+    <row r="124" spans="1:2">
+      <c r="A124" s="1">
+        <v>45716</v>
       </c>
       <c r="B124">
-        <v>2836.800048828125</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2">
-        <v>45717</v>
+        <v>2848.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" s="1">
+        <v>45747</v>
       </c>
       <c r="B125">
         <v>3122.800048828125</v>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2">
-        <v>45748</v>
+    <row r="126" spans="1:2">
+      <c r="A126" s="1">
+        <v>45777</v>
       </c>
       <c r="B126">
-        <v>3305</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2">
-        <v>45778</v>
+        <v>3319.10009765625</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" s="1">
+        <v>45808</v>
       </c>
       <c r="B127">
         <v>3288.89990234375</v>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2">
-        <v>45809</v>
+    <row r="128" spans="1:2">
+      <c r="A128" s="1">
+        <v>45838</v>
       </c>
       <c r="B128">
-        <v>3294.39990234375</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2">
-        <v>45839</v>
+        <v>3307.699951171875</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" s="1">
+        <v>45869</v>
       </c>
       <c r="B129">
         <v>3293.199951171875</v>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2">
-        <v>45870</v>
+    <row r="130" spans="1:2">
+      <c r="A130" s="1">
+        <v>45900</v>
       </c>
       <c r="B130">
-        <v>3473.699951171875</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2">
-        <v>45901</v>
+        <v>3516.10009765625</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" s="1">
+        <v>45930</v>
       </c>
       <c r="B131">
-        <v>3840.800048828125</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2">
-        <v>45931</v>
+        <v>3873.199951171875</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" s="1">
+        <v>45961</v>
       </c>
       <c r="B132">
-        <v>3982.199951171875</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2">
-        <v>45962</v>
+        <v>3996.5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" s="1">
+        <v>45991</v>
       </c>
       <c r="B133">
-        <v>4218.2998046875</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2">
-        <v>45992</v>
+        <v>4254.89990234375</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" s="1">
+        <v>46022</v>
       </c>
       <c r="B134">
-        <v>4325.60009765625</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2">
-        <v>46023</v>
+        <v>4341.10009765625</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" s="1">
+        <v>46053</v>
       </c>
       <c r="B135">
-        <v>4713.89990234375</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2">
-        <v>46054</v>
+        <v>4745.10009765625</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" s="1">
+        <v>46081</v>
       </c>
       <c r="B136">
-        <v>5230.5</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2">
-        <v>46082</v>
+        <v>5247.89990234375</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" s="1">
+        <v>46112</v>
       </c>
       <c r="B137">
         <v>4647.60009765625</v>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2">
-        <v>46113</v>
+    <row r="138" spans="1:2">
+      <c r="A138" s="1">
+        <v>46142</v>
       </c>
       <c r="B138">
-        <v>4614.7001953125</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2">
-        <v>46143</v>
+        <v>4629.60009765625</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" s="1">
+        <v>46173</v>
       </c>
       <c r="B139">
-        <v>4560.5</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2">
-        <v>46174</v>
+        <v>4593</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" s="1">
+        <v>46203</v>
       </c>
       <c r="B140">
-        <v>4022.89990234375</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2">
-        <v>46204</v>
+        <v>4038.5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" s="1">
+        <v>46234</v>
       </c>
       <c r="B141">
-        <v>4049.10009765625</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2">
-        <v>46235</v>
+        <v>4107</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" s="1">
+        <v>46265</v>
       </c>
       <c r="B142">
-        <v>4366</v>
+        <v>4481.5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B143">
+        <v>4186.7001953125</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" s="1">
+        <v>46326</v>
+      </c>
+      <c r="B144">
+        <v>4181.10009765625</v>
       </c>
     </row>
   </sheetData>
